--- a/исправления внести/si pi.xlsx
+++ b/исправления внести/si pi.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Rust\text_changer\исправления внести\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62222D0A-B0C5-482C-8073-407CC1E9AD55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBA797A3-3891-4D9B-BFD1-C7B09FBE1A00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1010" yWindow="1590" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>эквивалентных</t>
   </si>
@@ -49,19 +49,36 @@
   </si>
   <si>
     <t>сегменты</t>
+  </si>
+  <si>
+    <t>лабораторным</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
     </font>
   </fonts>
   <fills count="2">
@@ -84,8 +101,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -366,47 +385,55 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:A8"/>
+  <dimension ref="A1:A9"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="19.26953125" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
+    <row r="1" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+    <row r="2" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
+    <row r="3" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
+    <row r="4" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A4" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
+    <row r="5" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
+    <row r="6" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A6" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
+    <row r="7" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A7" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
+    <row r="8" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A8" s="2" t="s">
         <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A9" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/исправления внести/si pi.xlsx
+++ b/исправления внести/si pi.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Rust\text_changer\исправления внести\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBA797A3-3891-4D9B-BFD1-C7B09FBE1A00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{990AA690-C8FE-4748-A60C-EB5F5F27145F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-10530" yWindow="450" windowWidth="10710" windowHeight="20210" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -25,40 +25,100 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
-  <si>
-    <t>эквивалентных</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
   <si>
     <t>характеристикой</t>
   </si>
   <si>
-    <t>конденсаторы</t>
-  </si>
-  <si>
     <t>резисторы</t>
   </si>
   <si>
-    <t>моделируются</t>
-  </si>
-  <si>
     <t>транзисторы</t>
   </si>
   <si>
     <t>характеризуется</t>
   </si>
   <si>
-    <t>сегменты</t>
-  </si>
-  <si>
-    <t>лабораторным</t>
+    <t>доктор</t>
+  </si>
+  <si>
+    <t xml:space="preserve">программные </t>
+  </si>
+  <si>
+    <t>индуктивности</t>
+  </si>
+  <si>
+    <t xml:space="preserve">схемотехнического </t>
+  </si>
+  <si>
+    <t>программные продукты</t>
+  </si>
+  <si>
+    <t>меню</t>
+  </si>
+  <si>
+    <t xml:space="preserve">панелей </t>
+  </si>
+  <si>
+    <t xml:space="preserve">вентильное </t>
+  </si>
+  <si>
+    <t>запрограммированная</t>
+  </si>
+  <si>
+    <t>компонента</t>
+  </si>
+  <si>
+    <t>диске </t>
+  </si>
+  <si>
+    <t xml:space="preserve">панели </t>
+  </si>
+  <si>
+    <t xml:space="preserve">листа </t>
+  </si>
+  <si>
+    <t>шина</t>
+  </si>
+  <si>
+    <t>рельс</t>
+  </si>
+  <si>
+    <t>штампа</t>
+  </si>
+  <si>
+    <t>библиотечный </t>
+  </si>
+  <si>
+    <t>характеристику</t>
+  </si>
+  <si>
+    <t>модулированные</t>
+  </si>
+  <si>
+    <t>нано</t>
+  </si>
+  <si>
+    <t>микро</t>
+  </si>
+  <si>
+    <t>трапеций </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Панорамирование </t>
+  </si>
+  <si>
+    <t>металлизации</t>
+  </si>
+  <si>
+    <t>продолжение: Условное обозначение размеров</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -76,6 +136,13 @@
     <font>
       <sz val="12"/>
       <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF000000"/>
       <name val="Times New Roman"/>
       <family val="1"/>
       <charset val="204"/>
@@ -101,10 +168,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -385,55 +453,161 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:A9"/>
+  <dimension ref="A1:A31"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="19.26953125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
+      <c r="A1" s="2"/>
     </row>
     <row r="2" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A3" s="2" t="s">
-        <v>2</v>
-      </c>
+      <c r="A3" s="2"/>
     </row>
     <row r="4" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A10" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A11" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A12" s="2" t="s">
         <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A13" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A14" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A15" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A16" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A17" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A18" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A19" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A20" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A21" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A22" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A23" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A24" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A25" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A26" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A27" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A28" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A29" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A30" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A31" s="2" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>

--- a/исправления внести/si pi.xlsx
+++ b/исправления внести/si pi.xlsx
@@ -8,36 +8,35 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Rust\text_changer\исправления внести\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{990AA690-C8FE-4748-A60C-EB5F5F27145F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED337DAD-1721-4000-B545-94EC21D4726B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-10530" yWindow="450" windowWidth="10710" windowHeight="20210" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-11710" yWindow="390" windowWidth="10710" windowHeight="20210" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
-  <si>
-    <t>характеристикой</t>
-  </si>
-  <si>
-    <t>резисторы</t>
-  </si>
-  <si>
-    <t>транзисторы</t>
-  </si>
-  <si>
-    <t>характеризуется</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
   <si>
     <t>доктор</t>
   </si>
@@ -75,24 +74,15 @@
     <t xml:space="preserve">панели </t>
   </si>
   <si>
-    <t xml:space="preserve">листа </t>
-  </si>
-  <si>
     <t>шина</t>
   </si>
   <si>
     <t>рельс</t>
   </si>
   <si>
-    <t>штампа</t>
-  </si>
-  <si>
     <t>библиотечный </t>
   </si>
   <si>
-    <t>характеристику</t>
-  </si>
-  <si>
     <t>модулированные</t>
   </si>
   <si>
@@ -108,10 +98,61 @@
     <t xml:space="preserve">Панорамирование </t>
   </si>
   <si>
-    <t>металлизации</t>
-  </si>
-  <si>
-    <t>продолжение: Условное обозначение размеров</t>
+    <t>манипулятор</t>
+  </si>
+  <si>
+    <t xml:space="preserve">класс </t>
+  </si>
+  <si>
+    <t>механические</t>
+  </si>
+  <si>
+    <t>кодированные </t>
+  </si>
+  <si>
+    <t>система</t>
+  </si>
+  <si>
+    <t>профилирования </t>
+  </si>
+  <si>
+    <t>макрос</t>
+  </si>
+  <si>
+    <t xml:space="preserve">микросхема </t>
+  </si>
+  <si>
+    <t xml:space="preserve">подменю </t>
+  </si>
+  <si>
+    <t>диоды </t>
+  </si>
+  <si>
+    <t>буфера </t>
+  </si>
+  <si>
+    <t>осциллограмм</t>
+  </si>
+  <si>
+    <t>операционной </t>
+  </si>
+  <si>
+    <t>шифр</t>
+  </si>
+  <si>
+    <t>шифратор</t>
+  </si>
+  <si>
+    <t>модулятора </t>
+  </si>
+  <si>
+    <t>классификация </t>
+  </si>
+  <si>
+    <t>регистровом</t>
+  </si>
+  <si>
+    <t>макромодели</t>
   </si>
 </sst>
 </file>
@@ -453,31 +494,35 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:A31"/>
+  <dimension ref="A1:A39"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="19.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A1" s="2"/>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1" s="3" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="2" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A3" s="2"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A3" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="4" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
@@ -487,130 +532,173 @@
     </row>
     <row r="7" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
-        <v>3</v>
+        <v>21</v>
       </c>
     </row>
     <row r="8" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A9" s="1" t="s">
-        <v>5</v>
+      <c r="A9" s="2" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="10" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A11" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A11" s="3" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="12" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="14" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="17" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A18" s="3" t="s">
-        <v>14</v>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A18" s="1" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
-        <v>17</v>
+        <v>37</v>
       </c>
     </row>
     <row r="21" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A21" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A22" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A23" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A24" s="3" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A22" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A23" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A24" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A25" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A26" s="2" t="s">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A25" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A26" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A27" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A28" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A29" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A30" s="3" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="27" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A27" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A28" s="3" t="s">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A31" s="3" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="29" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A29" s="2" t="s">
+    <row r="32" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A32" s="2" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="30" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A30" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A31" s="2" t="s">
+    <row r="33" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A33" s="2" t="s">
         <v>28</v>
       </c>
     </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A34" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A35" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A36" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A37" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A38" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A39" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A1:A34">
+    <sortCondition ref="A1:A34"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/исправления внести/si pi.xlsx
+++ b/исправления внести/si pi.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Rust\text_changer\исправления внести\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED337DAD-1721-4000-B545-94EC21D4726B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{179C710D-E22C-457B-A3BC-3544A67091AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-11710" yWindow="390" windowWidth="10710" windowHeight="20210" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-13300" yWindow="0" windowWidth="13260" windowHeight="20690" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="51">
   <si>
     <t>доктор</t>
   </si>
@@ -146,20 +146,69 @@
     <t>модулятора </t>
   </si>
   <si>
-    <t>классификация </t>
-  </si>
-  <si>
     <t>регистровом</t>
   </si>
   <si>
     <t>макромодели</t>
+  </si>
+  <si>
+    <t>аппроксимирующей</t>
+  </si>
+  <si>
+    <t>коаксиального </t>
+  </si>
+  <si>
+    <t>корпорации</t>
+  </si>
+  <si>
+    <t>осциллографом</t>
+  </si>
+  <si>
+    <t>осциллограммы </t>
+  </si>
+  <si>
+    <t>лентой</t>
+  </si>
+  <si>
+    <t>система </t>
+  </si>
+  <si>
+    <t>шинных </t>
+  </si>
+  <si>
+    <t>технических </t>
+  </si>
+  <si>
+    <t>паспортных </t>
+  </si>
+  <si>
+    <t>продолжение</t>
+  </si>
+  <si>
+    <t>Переходные признаки одних и тех же радиоэлементов имеют емкостной нра</t>
+  </si>
+  <si>
+    <r>
+      <t>Собственная ёмкость </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="204"/>
+      </rPr>
+      <t>37</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -182,6 +231,14 @@
       <charset val="204"/>
     </font>
     <font>
+      <sz val="8"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <b/>
       <sz val="8"/>
       <color rgb="FF000000"/>
       <name val="Times New Roman"/>
@@ -494,7 +551,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:A39"/>
+  <dimension ref="A1:B50"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="19.26953125" customWidth="1"/>
@@ -597,7 +654,7 @@
     </row>
     <row r="20" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="21" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
@@ -687,12 +744,68 @@
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A38" s="3" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A39" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A40" s="3" t="s">
         <v>38</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A41" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A42" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A43" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A44" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A45" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A46" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A47" s="3" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A49" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A50" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>49</v>
       </c>
     </row>
   </sheetData>

--- a/исправления внести/si pi.xlsx
+++ b/исправления внести/si pi.xlsx
@@ -8,13 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Rust\text_changer\исправления внести\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{179C710D-E22C-457B-A3BC-3544A67091AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2369C286-1076-461C-88B4-58B94034C2A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-13300" yWindow="0" windowWidth="13260" windowHeight="20690" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38170" yWindow="0" windowWidth="28360" windowHeight="20690" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
+    <sheet name="после перевода" sheetId="2" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Лист1!$A$1:$A$60</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -36,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="71">
   <si>
     <t>доктор</t>
   </si>
@@ -156,9 +160,6 @@
   </si>
   <si>
     <t>коаксиального </t>
-  </si>
-  <si>
-    <t>корпорации</t>
   </si>
   <si>
     <t>осциллографом</t>
@@ -202,6 +203,69 @@
       </rPr>
       <t>37</t>
     </r>
+  </si>
+  <si>
+    <t>пара</t>
+  </si>
+  <si>
+    <t>ненулевым</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Такая случай </t>
+  </si>
+  <si>
+    <t>труднореализуемо</t>
+  </si>
+  <si>
+    <t>Распространённой применением</t>
+  </si>
+  <si>
+    <t xml:space="preserve">короткой прямых </t>
+  </si>
+  <si>
+    <t>этот утверждение</t>
+  </si>
+  <si>
+    <t>продвинутая подход</t>
+  </si>
+  <si>
+    <t>такой образ</t>
+  </si>
+  <si>
+    <t>полосковой прямые</t>
+  </si>
+  <si>
+    <t>микрополосковой прямые</t>
+  </si>
+  <si>
+    <t>осцилляций</t>
+  </si>
+  <si>
+    <t>к наименьшему их последствия</t>
+  </si>
+  <si>
+    <t>звонка проста</t>
+  </si>
+  <si>
+    <t xml:space="preserve">в одновременную чертёж </t>
+  </si>
+  <si>
+    <t>данная полномочие</t>
+  </si>
+  <si>
+    <t>ассиметричной прямые</t>
+  </si>
+  <si>
+    <t>Каждой прямые разностной пары</t>
+  </si>
+  <si>
+    <t>разностный полное сопротивление</t>
+  </si>
+  <si>
+    <t xml:space="preserve">реализуемо </t>
+  </si>
+  <si>
+    <t>обдумать</t>
   </si>
 </sst>
 </file>
@@ -266,11 +330,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -551,7 +616,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B50"/>
+  <dimension ref="A1:B60"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="19.26953125" customWidth="1"/>
@@ -717,101 +782,232 @@
         <v>26</v>
       </c>
     </row>
-    <row r="33" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A33" s="2" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A34" s="3" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A35" s="3" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A36" s="3" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A37" s="3" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A38" s="3" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.35">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A39" s="3" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A40" s="3" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A41" s="3" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A42" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A43" s="3" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A43" s="3" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A44" s="3" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A45" s="3" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A46" s="3" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A47" s="3" t="s">
         <v>46</v>
       </c>
+      <c r="B47" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A48" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A49" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="B49" s="3" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A50" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>49</v>
-      </c>
+        <v>51</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A51" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A52" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="B52" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A53" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A54" s="3"/>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A56" s="3"/>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A57" s="3"/>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A58" s="3"/>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A59" s="3"/>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A60" s="3"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:A60" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A1:A34">
     <sortCondition ref="A1:A34"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CBF60F53-632E-4247-9688-4A2BB13B53E2}">
+  <dimension ref="A1:A15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="36" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>68</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/исправления внести/si pi.xlsx
+++ b/исправления внести/si pi.xlsx
@@ -8,16 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Rust\text_changer\исправления внести\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2369C286-1076-461C-88B4-58B94034C2A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B13457F2-A5A2-45BF-BD18-C432A78E9F3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38170" yWindow="0" windowWidth="28360" windowHeight="20690" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-15210" yWindow="0" windowWidth="14600" windowHeight="20690" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
     <sheet name="после перевода" sheetId="2" r:id="rId2"/>
+    <sheet name="Лист2" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Лист1!$A$1:$A$60</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Лист1!$A$1:$A$51</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="57">
   <si>
     <t>доктор</t>
   </si>
@@ -150,16 +151,7 @@
     <t>модулятора </t>
   </si>
   <si>
-    <t>регистровом</t>
-  </si>
-  <si>
     <t>макромодели</t>
-  </si>
-  <si>
-    <t>аппроксимирующей</t>
-  </si>
-  <si>
-    <t>коаксиального </t>
   </si>
   <si>
     <t>осциллографом</t>
@@ -208,71 +200,38 @@
     <t>пара</t>
   </si>
   <si>
-    <t>ненулевым</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Такая случай </t>
-  </si>
-  <si>
-    <t>труднореализуемо</t>
-  </si>
-  <si>
-    <t>Распространённой применением</t>
-  </si>
-  <si>
-    <t xml:space="preserve">короткой прямых </t>
-  </si>
-  <si>
-    <t>этот утверждение</t>
-  </si>
-  <si>
-    <t>продвинутая подход</t>
-  </si>
-  <si>
-    <t>такой образ</t>
-  </si>
-  <si>
-    <t>полосковой прямые</t>
-  </si>
-  <si>
-    <t>микрополосковой прямые</t>
-  </si>
-  <si>
-    <t>осцилляций</t>
-  </si>
-  <si>
-    <t>к наименьшему их последствия</t>
-  </si>
-  <si>
-    <t>звонка проста</t>
-  </si>
-  <si>
-    <t xml:space="preserve">в одновременную чертёж </t>
-  </si>
-  <si>
-    <t>данная полномочие</t>
-  </si>
-  <si>
-    <t>ассиметричной прямые</t>
-  </si>
-  <si>
-    <t>Каждой прямые разностной пары</t>
-  </si>
-  <si>
-    <t>разностный полное сопротивление</t>
-  </si>
-  <si>
-    <t xml:space="preserve">реализуемо </t>
-  </si>
-  <si>
-    <t>обдумать</t>
+    <t>технич</t>
+  </si>
+  <si>
+    <t>в технической документации</t>
+  </si>
+  <si>
+    <t xml:space="preserve">профессору </t>
+  </si>
+  <si>
+    <t xml:space="preserve">техническую </t>
+  </si>
+  <si>
+    <t xml:space="preserve">подсистемы </t>
+  </si>
+  <si>
+    <t xml:space="preserve">техническом </t>
+  </si>
+  <si>
+    <t xml:space="preserve">шкала </t>
+  </si>
+  <si>
+    <t>швов</t>
+  </si>
+  <si>
+    <t>1.1 Частота и время 25</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -309,6 +268,27 @@
       <family val="1"/>
       <charset val="204"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3A3A3A"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -330,12 +310,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -616,7 +598,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B60"/>
+  <dimension ref="A1:B57"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="19.26953125" customWidth="1"/>
@@ -719,112 +701,112 @@
     </row>
     <row r="20" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
-        <v>36</v>
+        <v>13</v>
       </c>
     </row>
     <row r="21" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A21" s="2" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A23" s="2" t="s">
         <v>27</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A23" s="3" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A24" s="3" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A25" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A26" s="3" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A27" s="3" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="28" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A28" s="2" t="s">
+    <row r="27" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A27" s="2" t="s">
         <v>12</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A28" s="3" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A29" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A30" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A31" s="3" t="s">
         <v>25</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A31" s="2" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="32" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A32" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A33" s="2" t="s">
         <v>28</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A33" s="3" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A34" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A35" s="3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A36" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A37" s="3" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A38" s="3" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A39" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A40" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A41" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.35">
@@ -836,88 +818,85 @@
       <c r="A43" s="3" t="s">
         <v>42</v>
       </c>
+      <c r="B43" t="s">
+        <v>44</v>
+      </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A44" s="3" t="s">
         <v>43</v>
       </c>
+      <c r="B44" s="3" t="s">
+        <v>46</v>
+      </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A45" s="3" t="s">
         <v>44</v>
       </c>
+      <c r="B45" s="3" t="s">
+        <v>45</v>
+      </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A46" s="3" t="s">
-        <v>45</v>
+        <v>47</v>
+      </c>
+      <c r="B46" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A47" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A48" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A49" s="3" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A50" s="3" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A51" s="3" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A52" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="B52" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A52" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A53" s="3" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A54" s="3"/>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A55" s="3"/>
+    </row>
+    <row r="56" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A56" s="3"/>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A57" s="3"/>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A58" s="3"/>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A59" s="3"/>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A60" s="3"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:A60" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A1:A34">
-    <sortCondition ref="A1:A34"/>
+  <autoFilter ref="A1:A51" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A1:A33">
+    <sortCondition ref="A1:A33"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
@@ -926,86 +905,322 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CBF60F53-632E-4247-9688-4A2BB13B53E2}">
-  <dimension ref="A1:A15"/>
+  <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="36" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
-        <v>68</v>
-      </c>
+    <row r="1" spans="1:1" ht="18" x14ac:dyDescent="0.4">
+      <c r="A1" s="6" t="s">
+        <v>49</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{421BA651-CD18-4DF5-B0F9-B351900A5D03}">
+  <dimension ref="A1:B74"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="19.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.26953125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" s="4"/>
+      <c r="B1" s="5"/>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" s="4"/>
+      <c r="B2" s="4"/>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" s="4"/>
+      <c r="B3" s="5"/>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" s="4"/>
+      <c r="B4" s="5"/>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" s="4"/>
+      <c r="B5" s="5"/>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" s="4"/>
+      <c r="B6" s="5"/>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" s="4"/>
+      <c r="B7" s="5"/>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" s="4"/>
+      <c r="B8" s="5"/>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" s="4"/>
+      <c r="B9" s="5"/>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10" s="4"/>
+      <c r="B10" s="5"/>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A11" s="4"/>
+      <c r="B11" s="5"/>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A12" s="4"/>
+      <c r="B12" s="4"/>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A13" s="4"/>
+      <c r="B13" s="4"/>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A14" s="4"/>
+      <c r="B14" s="4"/>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A15" s="4"/>
+      <c r="B15" s="5"/>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A16" s="4"/>
+      <c r="B16" s="5"/>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A17" s="4"/>
+      <c r="B17" s="5"/>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A18" s="4"/>
+      <c r="B18" s="5"/>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A19" s="4"/>
+      <c r="B19" s="5"/>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A20" s="4"/>
+      <c r="B20" s="5"/>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A21" s="4"/>
+      <c r="B21" s="5"/>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A22" s="4"/>
+      <c r="B22" s="5"/>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A23" s="4"/>
+      <c r="B23" s="5"/>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A24" s="4"/>
+      <c r="B24" s="5"/>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A25" s="4"/>
+      <c r="B25" s="5"/>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A26" s="4"/>
+      <c r="B26" s="4"/>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A27" s="4"/>
+      <c r="B27" s="5"/>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A28" s="4"/>
+      <c r="B28" s="5"/>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A29" s="4"/>
+      <c r="B29" s="5"/>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A30" s="4"/>
+      <c r="B30" s="5"/>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A31" s="4"/>
+      <c r="B31" s="5"/>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A32" s="4"/>
+      <c r="B32" s="5"/>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A33" s="4"/>
+      <c r="B33" s="5"/>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A34" s="4"/>
+      <c r="B34" s="5"/>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A35" s="4"/>
+      <c r="B35" s="5"/>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A36" s="4"/>
+      <c r="B36" s="4"/>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A37" s="4"/>
+      <c r="B37" s="4"/>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A38" s="4"/>
+      <c r="B38" s="4"/>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A39" s="4"/>
+      <c r="B39" s="5"/>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A40" s="4"/>
+      <c r="B40" s="5"/>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A41" s="4"/>
+      <c r="B41" s="5"/>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A42" s="4"/>
+      <c r="B42" s="5"/>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A43" s="4"/>
+      <c r="B43" s="5"/>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A44" s="4"/>
+      <c r="B44" s="5"/>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A45" s="4"/>
+      <c r="B45" s="5"/>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A46" s="4"/>
+      <c r="B46" s="5"/>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A47" s="4"/>
+      <c r="B47" s="5"/>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A48" s="4"/>
+      <c r="B48" s="5"/>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A49" s="4"/>
+      <c r="B49" s="5"/>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A51" s="4"/>
+      <c r="B51" s="5"/>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A52" s="4"/>
+      <c r="B52" s="4"/>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A53" s="4"/>
+      <c r="B53" s="5"/>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A54" s="4"/>
+      <c r="B54" s="5"/>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A55" s="4"/>
+      <c r="B55" s="5"/>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A56" s="4"/>
+      <c r="B56" s="5"/>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A57" s="4"/>
+      <c r="B57" s="5"/>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A58" s="4"/>
+      <c r="B58" s="5"/>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A59" s="4"/>
+      <c r="B59" s="5"/>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A60" s="4"/>
+      <c r="B60" s="5"/>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A61" s="4"/>
+      <c r="B61" s="5"/>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A62" s="4"/>
+      <c r="B62" s="5"/>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A63" s="4"/>
+      <c r="B63" s="4"/>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A64" s="4"/>
+      <c r="B64" s="4"/>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A65" s="4"/>
+      <c r="B65" s="4"/>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A66" s="4"/>
+      <c r="B66" s="5"/>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A67" s="4"/>
+      <c r="B67" s="5"/>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A68" s="4"/>
+      <c r="B68" s="5"/>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A69" s="4"/>
+      <c r="B69" s="5"/>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A70" s="4"/>
+      <c r="B70" s="5"/>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A71" s="4"/>
+      <c r="B71" s="5"/>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A72" s="4"/>
+      <c r="B72" s="5"/>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A73" s="4"/>
+      <c r="B73" s="5"/>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A74" s="4"/>
+      <c r="B74" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/исправления внести/si pi.xlsx
+++ b/исправления внести/si pi.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Rust\text_changer\исправления внести\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B13457F2-A5A2-45BF-BD18-C432A78E9F3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4ABE44A-4C04-45E1-8CB3-B67E3BE06B33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-15210" yWindow="0" windowWidth="14600" windowHeight="20690" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-13120" yWindow="180" windowWidth="13260" windowHeight="20690" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="58">
   <si>
     <t>доктор</t>
   </si>
@@ -224,14 +224,17 @@
     <t>швов</t>
   </si>
   <si>
-    <t>1.1 Частота и время 25</t>
+    <t xml:space="preserve">текстуры </t>
+  </si>
+  <si>
+    <t>Пример 1.2. Измерение малой индуктивности по отношениюк земле</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -289,6 +292,14 @@
       <family val="1"/>
       <charset val="204"/>
     </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -310,7 +321,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -318,6 +329,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -838,12 +850,12 @@
         <v>45</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:2" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A46" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="B46" t="s">
-        <v>56</v>
+      <c r="B46" s="7" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.35">
@@ -882,7 +894,9 @@
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A54" s="3"/>
+      <c r="A54" s="3" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A55" s="3"/>

--- a/исправления внести/si pi.xlsx
+++ b/исправления внести/si pi.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Rust\text_changer\исправления внести\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4ABE44A-4C04-45E1-8CB3-B67E3BE06B33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{612AF120-B876-4021-B4BC-EB53E423BA9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-13120" yWindow="180" windowWidth="13260" windowHeight="20690" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-16960" yWindow="0" windowWidth="16620" windowHeight="20690" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="55">
   <si>
     <t>доктор</t>
   </si>
@@ -58,9 +58,6 @@
     <t>программные продукты</t>
   </si>
   <si>
-    <t>меню</t>
-  </si>
-  <si>
     <t xml:space="preserve">панелей </t>
   </si>
   <si>
@@ -178,25 +175,6 @@
     <t>продолжение</t>
   </si>
   <si>
-    <t>Переходные признаки одних и тех же радиоэлементов имеют емкостной нра</t>
-  </si>
-  <si>
-    <r>
-      <t>Собственная ёмкость </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="8"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="204"/>
-      </rPr>
-      <t>37</t>
-    </r>
-  </si>
-  <si>
     <t>пара</t>
   </si>
   <si>
@@ -224,17 +202,17 @@
     <t>швов</t>
   </si>
   <si>
-    <t xml:space="preserve">текстуры </t>
-  </si>
-  <si>
-    <t>Пример 1.2. Измерение малой индуктивности по отношениюк земле</t>
+    <t xml:space="preserve">экспоненциального </t>
+  </si>
+  <si>
+    <t>Рассчёт (1.32) является первым приближением существенной величин</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -257,14 +235,6 @@
       <charset val="204"/>
     </font>
     <font>
-      <sz val="8"/>
-      <color rgb="FF000000"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-      <charset val="204"/>
-    </font>
-    <font>
-      <b/>
       <sz val="8"/>
       <color rgb="FF000000"/>
       <name val="Times New Roman"/>
@@ -326,10 +296,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -610,7 +580,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B57"/>
+  <dimension ref="A1:B74"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="19.26953125" customWidth="1"/>
@@ -618,17 +588,17 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
@@ -638,7 +608,7 @@
     </row>
     <row r="5" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
@@ -648,57 +618,55 @@
     </row>
     <row r="7" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A10" s="2" t="s">
-        <v>5</v>
-      </c>
+      <c r="A10" s="2"/>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="14" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="18" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
@@ -713,7 +681,7 @@
     </row>
     <row r="20" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="21" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
@@ -723,189 +691,224 @@
     </row>
     <row r="22" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A23" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A24" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A25" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A26" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="27" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A27" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A28" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A29" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A30" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="31" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A31" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="32" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A32" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A33" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A34" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A35" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A36" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A37" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A38" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A39" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A40" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A41" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A42" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A43" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B43" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A44" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B43" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A44" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>46</v>
+      <c r="B44" s="1" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A45" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>45</v>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="B45" s="3"/>
     </row>
     <row r="46" spans="1:2" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A46" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="B46" s="7" t="s">
-        <v>57</v>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="B46" s="7"/>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A47" s="3" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A48" s="3" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A49" s="3" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A50" s="3" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A51" s="3" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A52" s="3" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A53" s="3" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A54" s="3" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A55" s="3"/>
+        <v>53</v>
+      </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A56" s="3"/>
     </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A57" s="3"/>
+    <row r="58" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A58" s="3"/>
+    </row>
+    <row r="59" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A59" s="3"/>
+    </row>
+    <row r="61" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A61" s="3"/>
+    </row>
+    <row r="62" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A62" s="3"/>
+    </row>
+    <row r="63" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A63" s="3"/>
+    </row>
+    <row r="64" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A64" s="3"/>
+    </row>
+    <row r="65" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A65" s="3"/>
+    </row>
+    <row r="66" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A66" s="3"/>
+    </row>
+    <row r="67" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A67" s="3"/>
+    </row>
+    <row r="68" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A68" s="3"/>
+    </row>
+    <row r="69" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A69" s="3"/>
+    </row>
+    <row r="70" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A70" s="3"/>
+    </row>
+    <row r="71" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A71" s="3"/>
+    </row>
+    <row r="73" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A73" s="3"/>
+    </row>
+    <row r="74" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A74" s="3"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:A51" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
@@ -919,19 +922,30 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CBF60F53-632E-4247-9688-4A2BB13B53E2}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:A17"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="36" customWidth="1"/>
+    <col min="1" max="1" width="59.1796875" customWidth="1"/>
+    <col min="2" max="2" width="35.26953125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1" ht="18" x14ac:dyDescent="0.4">
       <c r="A1" s="6" t="s">
-        <v>49</v>
-      </c>
+        <v>46</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A6" s="1"/>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A9" s="3"/>
+    </row>
+    <row r="17" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A17" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/исправления внести/si pi.xlsx
+++ b/исправления внести/si pi.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Rust\text_changer\исправления внести\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{612AF120-B876-4021-B4BC-EB53E423BA9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBDCE087-9A70-4CE5-B13C-D461BA8DF536}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-16960" yWindow="0" windowWidth="16620" windowHeight="20690" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38510" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
     <sheet name="после перевода" sheetId="2" r:id="rId2"/>
-    <sheet name="Лист2" sheetId="3" r:id="rId3"/>
+    <sheet name="слова применить" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Лист1!$A$1:$A$51</definedName>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="61">
   <si>
     <t>доктор</t>
   </si>
@@ -206,6 +206,24 @@
   </si>
   <si>
     <t>Рассчёт (1.32) является первым приближением существенной величин</t>
+  </si>
+  <si>
+    <t>сценариях</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ресурсоемкими </t>
+  </si>
+  <si>
+    <t>монитора</t>
+  </si>
+  <si>
+    <t xml:space="preserve">дисплеем </t>
+  </si>
+  <si>
+    <t>масштабируется</t>
+  </si>
+  <si>
+    <t>изыск</t>
   </si>
 </sst>
 </file>
@@ -862,14 +880,30 @@
         <v>53</v>
       </c>
     </row>
+    <row r="55" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A55" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A56" s="3"/>
+      <c r="A56" s="3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A57" s="3" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A58" s="3"/>
+      <c r="A58" s="3" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A59" s="3"/>
+      <c r="A59" s="3" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A61" s="3"/>
@@ -1043,7 +1077,9 @@
       <c r="B21" s="5"/>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A22" s="4"/>
+      <c r="A22" s="4" t="s">
+        <v>60</v>
+      </c>
       <c r="B22" s="5"/>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.35">

--- a/исправления внести/si pi.xlsx
+++ b/исправления внести/si pi.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Rust\text_changer\исправления внести\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBDCE087-9A70-4CE5-B13C-D461BA8DF536}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53A36143-12D1-4A32-9885-6CCB51BC3587}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38510" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38510" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="64">
   <si>
     <t>доктор</t>
   </si>
@@ -220,10 +220,19 @@
     <t xml:space="preserve">дисплеем </t>
   </si>
   <si>
-    <t>масштабируется</t>
-  </si>
-  <si>
     <t>изыск</t>
+  </si>
+  <si>
+    <t xml:space="preserve">эмпирических </t>
+  </si>
+  <si>
+    <t xml:space="preserve">индуцированы </t>
+  </si>
+  <si>
+    <t xml:space="preserve">индуктивным </t>
+  </si>
+  <si>
+    <t>пара это равный</t>
   </si>
 </sst>
 </file>
@@ -902,14 +911,23 @@
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A59" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A60" s="3" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A61" s="3"/>
+      <c r="A61" s="3" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A62" s="3"/>
+      <c r="A62" s="3" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A63" s="3"/>
@@ -1078,7 +1096,7 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B22" s="5"/>
     </row>

--- a/исправления внести/si pi.xlsx
+++ b/исправления внести/si pi.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Rust\text_changer\исправления внести\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53A36143-12D1-4A32-9885-6CCB51BC3587}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27EA19B8-5DEE-448D-9403-08B649364F70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38510" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,7 @@
     <sheet name="слова применить" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Лист1!$A$1:$A$51</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Лист1!$A$1:$A$54</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="56">
   <si>
     <t>доктор</t>
   </si>
@@ -61,9 +61,6 @@
     <t xml:space="preserve">панелей </t>
   </si>
   <si>
-    <t xml:space="preserve">вентильное </t>
-  </si>
-  <si>
     <t>запрограммированная</t>
   </si>
   <si>
@@ -85,9 +82,6 @@
     <t>библиотечный </t>
   </si>
   <si>
-    <t>модулированные</t>
-  </si>
-  <si>
     <t>нано</t>
   </si>
   <si>
@@ -145,9 +139,6 @@
     <t>шифратор</t>
   </si>
   <si>
-    <t>модулятора </t>
-  </si>
-  <si>
     <t>макромодели</t>
   </si>
   <si>
@@ -175,9 +166,6 @@
     <t>продолжение</t>
   </si>
   <si>
-    <t>пара</t>
-  </si>
-  <si>
     <t>технич</t>
   </si>
   <si>
@@ -196,9 +184,6 @@
     <t xml:space="preserve">техническом </t>
   </si>
   <si>
-    <t xml:space="preserve">шкала </t>
-  </si>
-  <si>
     <t>швов</t>
   </si>
   <si>
@@ -208,9 +193,6 @@
     <t>Рассчёт (1.32) является первым приближением существенной величин</t>
   </si>
   <si>
-    <t>сценариях</t>
-  </si>
-  <si>
     <t xml:space="preserve">ресурсоемкими </t>
   </si>
   <si>
@@ -223,16 +205,10 @@
     <t>изыск</t>
   </si>
   <si>
-    <t xml:space="preserve">эмпирических </t>
-  </si>
-  <si>
     <t xml:space="preserve">индуцированы </t>
   </si>
   <si>
     <t xml:space="preserve">индуктивным </t>
-  </si>
-  <si>
-    <t>пара это равный</t>
   </si>
 </sst>
 </file>
@@ -615,17 +591,15 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A2" s="2" t="s">
-        <v>6</v>
-      </c>
+      <c r="A2" s="2"/>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
@@ -635,7 +609,7 @@
     </row>
     <row r="5" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
@@ -645,17 +619,17 @@
     </row>
     <row r="7" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
@@ -663,22 +637,20 @@
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A13" s="2" t="s">
-        <v>14</v>
-      </c>
+      <c r="A13" s="2"/>
     </row>
     <row r="14" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
@@ -688,12 +660,12 @@
     </row>
     <row r="16" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
@@ -708,7 +680,7 @@
     </row>
     <row r="20" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
@@ -718,216 +690,204 @@
     </row>
     <row r="22" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A23" s="3" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A24" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A25" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A26" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="27" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A27" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A28" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A29" s="3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A30" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="31" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A31" s="2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="32" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A32" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A33" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A34" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A35" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A36" s="3" t="s">
-        <v>34</v>
-      </c>
+      <c r="A36" s="3"/>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A37" s="3" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A38" s="3" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A39" s="3" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A40" s="3" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A41" s="3" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A42" s="3" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A43" s="3" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B43" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
     <row r="44" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A44" s="3" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A45" s="3" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B45" s="3"/>
     </row>
     <row r="46" spans="1:2" ht="17.5" x14ac:dyDescent="0.35">
-      <c r="A46" s="3" t="s">
-        <v>44</v>
-      </c>
+      <c r="A46" s="3"/>
       <c r="B46" s="7"/>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A47" s="3" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A48" s="3" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A49" s="3" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A50" s="3" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A51" s="3" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A52" s="3" t="s">
-        <v>51</v>
-      </c>
+      <c r="A52" s="3"/>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A53" s="3" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A54" s="3" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A55" s="3" t="s">
-        <v>55</v>
-      </c>
+      <c r="A55" s="3"/>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A56" s="3" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A57" s="3" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A58" s="3" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A59" s="3" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A60" s="3" t="s">
-        <v>60</v>
-      </c>
+      <c r="A60" s="3"/>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A61" s="3" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A62" s="3" t="s">
-        <v>63</v>
-      </c>
+      <c r="A62" s="3"/>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A63" s="3"/>
@@ -963,7 +923,7 @@
       <c r="A74" s="3"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:A51" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:A54" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A1:A33">
     <sortCondition ref="A1:A33"/>
   </sortState>
@@ -983,7 +943,7 @@
   <sheetData>
     <row r="1" spans="1:1" ht="18" x14ac:dyDescent="0.4">
       <c r="A1" s="6" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
     </row>
     <row r="6" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
@@ -1096,7 +1056,7 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" s="4" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="B22" s="5"/>
     </row>
